--- a/data/uploads/All Projects 2 6-4-2026 10-57-13 AM.xlsx
+++ b/data/uploads/All Projects 2 6-4-2026 10-57-13 AM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SA1507\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{049696D5-2A6F-4917-86D8-965961FAE2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F35B8A-031B-446B-8639-60D218D00945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3645,7 +3645,7 @@
         <v>139</v>
       </c>
       <c r="U14" s="2">
-        <v>45904.592037037037</v>
+        <v>45904.59134259259</v>
       </c>
       <c r="W14" s="4">
         <v>0</v>

--- a/data/uploads/All Projects 2 6-4-2026 10-57-13 AM.xlsx
+++ b/data/uploads/All Projects 2 6-4-2026 10-57-13 AM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SA1507\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F35B8A-031B-446B-8639-60D218D00945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8AD48AD-B126-4DEF-97EA-244A0DB04F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3645,7 +3645,7 @@
         <v>139</v>
       </c>
       <c r="U14" s="2">
-        <v>45904.59134259259</v>
+        <v>45904.592037037037</v>
       </c>
       <c r="W14" s="4">
         <v>0</v>

--- a/data/uploads/All Projects 2 6-4-2026 10-57-13 AM.xlsx
+++ b/data/uploads/All Projects 2 6-4-2026 10-57-13 AM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SA1507\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8AD48AD-B126-4DEF-97EA-244A0DB04F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8FB4249-C79B-4E49-AC4C-31BD055472A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3645,7 +3645,7 @@
         <v>139</v>
       </c>
       <c r="U14" s="2">
-        <v>45904.592037037037</v>
+        <v>45904.59134259259</v>
       </c>
       <c r="W14" s="4">
         <v>0</v>
